--- a/results/recurrence/glass_recurrence_score_standard_treatment.xlsx
+++ b/results/recurrence/glass_recurrence_score_standard_treatment.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,26 +414,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>PATIENT_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>First Recurrence</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tumor Primary</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>DELTA_RECURRENCE_SCORE</t>
         </is>
@@ -458,10 +446,10 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.240397942741943</v>
+      </c>
+      <c r="C2" t="n">
         <v>-0.1500761234768785</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.240397942741943</v>
       </c>
       <c r="D2" t="n">
         <v>0.3904740662188216</v>
@@ -474,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.4213211981181357</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0.2764734625958086</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.4213211981181357</v>
       </c>
       <c r="D3" t="n">
         <v>0.6977946607139442</v>
@@ -490,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.1041018816463418</v>
+      </c>
+      <c r="C4" t="n">
         <v>-0.2389124700544564</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1041018816463418</v>
       </c>
       <c r="D4" t="n">
         <v>0.3430143517007982</v>
@@ -506,10 +494,10 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.1142460350346406</v>
+      </c>
+      <c r="C5" t="n">
         <v>-0.149983326062978</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1142460350346406</v>
       </c>
       <c r="D5" t="n">
         <v>0.2642293610976186</v>
@@ -522,10 +510,10 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.2841583568809227</v>
+      </c>
+      <c r="C6" t="n">
         <v>-0.2845214296518401</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.2841583568809227</v>
       </c>
       <c r="D6" t="n">
         <v>0.5686797865327629</v>
@@ -538,10 +526,10 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>-0.1693598200285555</v>
+      </c>
+      <c r="C7" t="n">
         <v>-0.2119463198024141</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.1693598200285555</v>
       </c>
       <c r="D7" t="n">
         <v>0.04258649977385859</v>
@@ -554,10 +542,10 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.1745181502648471</v>
+      </c>
+      <c r="C8" t="n">
         <v>-0.313748353062365</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.1745181502648471</v>
       </c>
       <c r="D8" t="n">
         <v>0.4882665033272121</v>
@@ -570,10 +558,10 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.4431521062380919</v>
+      </c>
+      <c r="C9" t="n">
         <v>-0.2535692991396751</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.4431521062380919</v>
       </c>
       <c r="D9" t="n">
         <v>0.6967214053777669</v>
@@ -586,10 +574,10 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-0.1199295756593415</v>
+      </c>
+      <c r="C10" t="n">
         <v>-0.1459773140351692</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.1199295756593415</v>
       </c>
       <c r="D10" t="n">
         <v>0.02604773837582769</v>
@@ -602,10 +590,10 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-0.06818193829026142</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.338679588595303</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.06818193829026142</v>
       </c>
       <c r="D11" t="n">
         <v>-0.4068615268855644</v>
@@ -618,10 +606,10 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-0.2155618399951673</v>
+      </c>
+      <c r="C12" t="n">
         <v>-0.08361289843555031</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.2155618399951673</v>
       </c>
       <c r="D12" t="n">
         <v>-0.131948941559617</v>
@@ -634,10 +622,10 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-0.2254429466417733</v>
+      </c>
+      <c r="C13" t="n">
         <v>-0.2735750275974079</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.2254429466417733</v>
       </c>
       <c r="D13" t="n">
         <v>0.04813208095563454</v>
@@ -650,10 +638,10 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>-0.1858585144416247</v>
+      </c>
+      <c r="C14" t="n">
         <v>-0.3121996700922749</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.1858585144416247</v>
       </c>
       <c r="D14" t="n">
         <v>0.1263411556506502</v>
@@ -666,10 +654,10 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0.2822901815320389</v>
+      </c>
+      <c r="C15" t="n">
         <v>-0.2575719702398097</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.2822901815320389</v>
       </c>
       <c r="D15" t="n">
         <v>0.5398621517718485</v>
@@ -682,10 +670,10 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0.282052994639917</v>
+      </c>
+      <c r="C16" t="n">
         <v>0.1512829934976888</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.282052994639917</v>
       </c>
       <c r="D16" t="n">
         <v>0.1307700011422282</v>
@@ -698,10 +686,10 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0.1777577531392439</v>
+      </c>
+      <c r="C17" t="n">
         <v>-0.3901546342078486</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.1777577531392439</v>
       </c>
       <c r="D17" t="n">
         <v>0.5679123873470925</v>
@@ -714,10 +702,10 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0.1012182419383847</v>
+      </c>
+      <c r="C18" t="n">
         <v>-0.2928248716000603</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.1012182419383847</v>
       </c>
       <c r="D18" t="n">
         <v>0.394043113538445</v>
@@ -730,10 +718,10 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>-0.1916952565215667</v>
+      </c>
+      <c r="C19" t="n">
         <v>-0.3792681687753456</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.1916952565215667</v>
       </c>
       <c r="D19" t="n">
         <v>0.1875729122537789</v>
@@ -746,10 +734,10 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0.008528727755699905</v>
+      </c>
+      <c r="C20" t="n">
         <v>-0.2358586931303739</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.008528727755699905</v>
       </c>
       <c r="D20" t="n">
         <v>0.2443874208860738</v>
@@ -762,10 +750,10 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0.1271008208560982</v>
+      </c>
+      <c r="C21" t="n">
         <v>0.01248015692487348</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.1271008208560982</v>
       </c>
       <c r="D21" t="n">
         <v>0.1146206639312247</v>
@@ -778,10 +766,10 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>0.1854433873613601</v>
+      </c>
+      <c r="C22" t="n">
         <v>0.190599868617545</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.1854433873613601</v>
       </c>
       <c r="D22" t="n">
         <v>-0.005156481256184897</v>
@@ -794,10 +782,10 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>0.2120321680177605</v>
+      </c>
+      <c r="C23" t="n">
         <v>-0.263503400108836</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.2120321680177605</v>
       </c>
       <c r="D23" t="n">
         <v>0.4755355681265965</v>
@@ -810,10 +798,10 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>-0.04550521491040738</v>
+      </c>
+      <c r="C24" t="n">
         <v>-0.01180110863191397</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.04550521491040738</v>
       </c>
       <c r="D24" t="n">
         <v>-0.03370410627849341</v>
@@ -826,10 +814,10 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-0.1081878379166377</v>
+      </c>
+      <c r="C25" t="n">
         <v>-0.2524390807279341</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.1081878379166377</v>
       </c>
       <c r="D25" t="n">
         <v>0.1442512428112965</v>
@@ -842,10 +830,10 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0.09548493753193116</v>
+      </c>
+      <c r="C26" t="n">
         <v>-0.2842593539696623</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.09548493753193116</v>
       </c>
       <c r="D26" t="n">
         <v>0.3797442915015935</v>
@@ -858,10 +846,10 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>-0.01522654780539456</v>
+      </c>
+      <c r="C27" t="n">
         <v>-0.3451595291067139</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.01522654780539456</v>
       </c>
       <c r="D27" t="n">
         <v>0.3299329813013194</v>
@@ -874,10 +862,10 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0.2027758303693769</v>
+      </c>
+      <c r="C28" t="n">
         <v>-0.2064253790402321</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.2027758303693769</v>
       </c>
       <c r="D28" t="n">
         <v>0.409201209409609</v>
@@ -890,10 +878,10 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0.294537277274133</v>
+      </c>
+      <c r="C29" t="n">
         <v>-0.1787230932344356</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.294537277274133</v>
       </c>
       <c r="D29" t="n">
         <v>0.4732603705085686</v>
@@ -906,10 +894,10 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>0.1904859131449045</v>
+      </c>
+      <c r="C30" t="n">
         <v>-0.1166735285906</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.1904859131449045</v>
       </c>
       <c r="D30" t="n">
         <v>0.3071594417355045</v>
@@ -922,10 +910,10 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>0.009123982064009883</v>
+      </c>
+      <c r="C31" t="n">
         <v>0.237884575098714</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.009123982064009883</v>
       </c>
       <c r="D31" t="n">
         <v>-0.2287605930347041</v>
@@ -938,10 +926,10 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>-0.001284185675907046</v>
+      </c>
+      <c r="C32" t="n">
         <v>-0.23761454121298</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.001284185675907046</v>
       </c>
       <c r="D32" t="n">
         <v>0.2363303555370729</v>
@@ -954,10 +942,10 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>0.02517382103302068</v>
+      </c>
+      <c r="C33" t="n">
         <v>-0.1707181460121928</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.02517382103302068</v>
       </c>
       <c r="D33" t="n">
         <v>0.1958919670452135</v>
@@ -970,10 +958,10 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>-0.1785080906540044</v>
+      </c>
+      <c r="C34" t="n">
         <v>-0.1480870037865181</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.1785080906540044</v>
       </c>
       <c r="D34" t="n">
         <v>-0.03042108686748635</v>
@@ -986,10 +974,10 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>-0.06561323405303643</v>
+      </c>
+      <c r="C35" t="n">
         <v>-0.1498781359978958</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.06561323405303643</v>
       </c>
       <c r="D35" t="n">
         <v>0.08426490194485942</v>
@@ -1002,10 +990,10 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>-0.01643027180035167</v>
+      </c>
+      <c r="C36" t="n">
         <v>-0.169674736526544</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.01643027180035167</v>
       </c>
       <c r="D36" t="n">
         <v>0.1532444647261924</v>
@@ -1018,10 +1006,10 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>-0.1676058002285175</v>
+      </c>
+      <c r="C37" t="n">
         <v>-0.2448343928541279</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.1676058002285175</v>
       </c>
       <c r="D37" t="n">
         <v>0.07722859262561046</v>
@@ -1034,10 +1022,10 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>0.2181889285389335</v>
+      </c>
+      <c r="C38" t="n">
         <v>-0.3547268645191287</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.2181889285389335</v>
       </c>
       <c r="D38" t="n">
         <v>0.5729157930580622</v>
@@ -1050,10 +1038,10 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>0.2600100505867158</v>
+      </c>
+      <c r="C39" t="n">
         <v>-0.09443705220358006</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.2600100505867158</v>
       </c>
       <c r="D39" t="n">
         <v>0.3544471027902958</v>
@@ -1066,10 +1054,10 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>0.03390607113445931</v>
+      </c>
+      <c r="C40" t="n">
         <v>-0.2002254589768854</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.03390607113445931</v>
       </c>
       <c r="D40" t="n">
         <v>0.2341315301113447</v>
@@ -1082,10 +1070,10 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>0.0746377178750538</v>
+      </c>
+      <c r="C41" t="n">
         <v>-0.3059115785148844</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.0746377178750538</v>
       </c>
       <c r="D41" t="n">
         <v>0.3805492963899382</v>
@@ -1098,10 +1086,10 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>-0.3173394691324223</v>
+      </c>
+      <c r="C42" t="n">
         <v>-0.2860545135770747</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.3173394691324223</v>
       </c>
       <c r="D42" t="n">
         <v>-0.0312849555553476</v>
@@ -1114,10 +1102,10 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>0.008891900564720001</v>
+      </c>
+      <c r="C43" t="n">
         <v>-0.1984815447500237</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.008891900564720001</v>
       </c>
       <c r="D43" t="n">
         <v>0.2073734453147437</v>
@@ -1130,10 +1118,10 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>0.2940113528206453</v>
+      </c>
+      <c r="C44" t="n">
         <v>-0.170178435273264</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.2940113528206453</v>
       </c>
       <c r="D44" t="n">
         <v>0.4641897880939093</v>
@@ -1146,10 +1134,10 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>-0.2328361142960023</v>
+      </c>
+      <c r="C45" t="n">
         <v>-0.2222798729160098</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.2328361142960023</v>
       </c>
       <c r="D45" t="n">
         <v>-0.01055624137999256</v>
@@ -1162,10 +1150,10 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>-0.2299466189094423</v>
+      </c>
+      <c r="C46" t="n">
         <v>-0.3925134343582948</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.2299466189094423</v>
       </c>
       <c r="D46" t="n">
         <v>0.1625668154488525</v>
@@ -1178,10 +1166,10 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>-0.171768430530216</v>
+      </c>
+      <c r="C47" t="n">
         <v>0.0535955550021493</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.171768430530216</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2253639855323653</v>
@@ -1194,10 +1182,10 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>0.01702883081564349</v>
+      </c>
+      <c r="C48" t="n">
         <v>0.1187629347542111</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.01702883081564349</v>
       </c>
       <c r="D48" t="n">
         <v>-0.1017341039385676</v>
@@ -1210,10 +1198,10 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>0.403528959292164</v>
+      </c>
+      <c r="C49" t="n">
         <v>-0.138173420977198</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.403528959292164</v>
       </c>
       <c r="D49" t="n">
         <v>0.5417023802693621</v>
@@ -1226,10 +1214,10 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>-0.1189164035526579</v>
+      </c>
+      <c r="C50" t="n">
         <v>-0.1167391742835678</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.1189164035526579</v>
       </c>
       <c r="D50" t="n">
         <v>-0.002177229269090031</v>
@@ -1242,10 +1230,10 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>0.3217665587828171</v>
+      </c>
+      <c r="C51" t="n">
         <v>-0.2362411491461037</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.3217665587828171</v>
       </c>
       <c r="D51" t="n">
         <v>0.5580077079289207</v>
@@ -1258,10 +1246,10 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>-0.2381180692050073</v>
+      </c>
+      <c r="C52" t="n">
         <v>-0.3271473806588898</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.2381180692050073</v>
       </c>
       <c r="D52" t="n">
         <v>0.08902931145388249</v>
@@ -1274,10 +1262,10 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>-0.1593925529787303</v>
+      </c>
+      <c r="C53" t="n">
         <v>-0.1311696188669709</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.1593925529787303</v>
       </c>
       <c r="D53" t="n">
         <v>-0.02822293411175941</v>
@@ -1290,10 +1278,10 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>0.02421054206770556</v>
+      </c>
+      <c r="C54" t="n">
         <v>-0.3119282977657173</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.02421054206770556</v>
       </c>
       <c r="D54" t="n">
         <v>0.3361388398334229</v>
@@ -1306,10 +1294,10 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>-0.3683494893489501</v>
+      </c>
+      <c r="C55" t="n">
         <v>-0.3318708521615391</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.3683494893489501</v>
       </c>
       <c r="D55" t="n">
         <v>-0.03647863718741096</v>
@@ -1322,10 +1310,10 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>0.07740936665173415</v>
+      </c>
+      <c r="C56" t="n">
         <v>-0.0366035140612041</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.07740936665173415</v>
       </c>
       <c r="D56" t="n">
         <v>0.1140128807129382</v>
@@ -1338,10 +1326,10 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>-0.2299061879927619</v>
+      </c>
+      <c r="C57" t="n">
         <v>-0.3855777392233229</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.2299061879927619</v>
       </c>
       <c r="D57" t="n">
         <v>0.155671551230561</v>
@@ -1354,10 +1342,10 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>0.04409624032524612</v>
+      </c>
+      <c r="C58" t="n">
         <v>-0.2348577567185383</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.04409624032524612</v>
       </c>
       <c r="D58" t="n">
         <v>0.2789539970437844</v>
@@ -1370,10 +1358,10 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>-0.1693948040430185</v>
+      </c>
+      <c r="C59" t="n">
         <v>-0.2262223090047014</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.1693948040430185</v>
       </c>
       <c r="D59" t="n">
         <v>0.05682750496168287</v>
@@ -1386,10 +1374,10 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>-0.3584373639913</v>
+      </c>
+      <c r="C60" t="n">
         <v>-0.09053534887067188</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.3584373639913</v>
       </c>
       <c r="D60" t="n">
         <v>-0.2679020151206281</v>
@@ -1402,10 +1390,10 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>-0.1597541493252341</v>
+      </c>
+      <c r="C61" t="n">
         <v>-0.203923831416286</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.1597541493252341</v>
       </c>
       <c r="D61" t="n">
         <v>0.04416968209105182</v>
@@ -1418,10 +1406,10 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>0.06591725674659032</v>
+      </c>
+      <c r="C62" t="n">
         <v>-0.1671454317786639</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.06591725674659032</v>
       </c>
       <c r="D62" t="n">
         <v>0.2330626885252542</v>
@@ -1434,10 +1422,10 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>0.2925491890111084</v>
+      </c>
+      <c r="C63" t="n">
         <v>-0.3291747442260283</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.2925491890111084</v>
       </c>
       <c r="D63" t="n">
         <v>0.6217239332371367</v>
@@ -1450,10 +1438,10 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>0.1863883679778391</v>
+      </c>
+      <c r="C64" t="n">
         <v>-0.2353337552595551</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.1863883679778391</v>
       </c>
       <c r="D64" t="n">
         <v>0.4217221232373942</v>
@@ -1462,320 +1450,368 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GLSS-SM-R099</t>
+          <t>GLSS-SM-R095</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.1421079540557695</v>
+        <v>0.3354024800563348</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2032358262635371</v>
+        <v>-0.2674284726875144</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3453437803193067</v>
+        <v>0.6028309527438491</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GLSS-SM-R100</t>
+          <t>GLSS-SM-R099</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.1917551586475986</v>
+        <v>0.2032358262635371</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.03854988988495561</v>
+        <v>-0.1421079540557695</v>
       </c>
       <c r="D66" t="n">
-        <v>0.153205268762643</v>
+        <v>0.3453437803193067</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GLSS-SM-R102</t>
+          <t>GLSS-SM-R100</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.0773780374776124</v>
+        <v>-0.03854988988495561</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1717473000681943</v>
+        <v>-0.1917551586475986</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.09436926259058187</v>
+        <v>0.153205268762643</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GLSS-SM-R103</t>
+          <t>GLSS-SM-R102</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.2750077146625198</v>
+        <v>-0.1717473000681943</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2540674285237414</v>
+        <v>-0.0773780374776124</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5290751431862613</v>
+        <v>-0.09436926259058187</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GLSS-SM-R104</t>
+          <t>GLSS-SM-R103</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.2563746745553541</v>
+        <v>0.2540674285237414</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3031334859045485</v>
+        <v>-0.2750077146625198</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5595081604599026</v>
+        <v>0.5290751431862613</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GLSS-SM-R106</t>
+          <t>GLSS-SM-R104</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.2823241496423203</v>
+        <v>0.3031334859045485</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.1181004962359042</v>
+        <v>-0.2563746745553541</v>
       </c>
       <c r="D70" t="n">
-        <v>0.164223653406416</v>
+        <v>0.5595081604599026</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GLSS-SM-R107</t>
+          <t>GLSS-SM-R106</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.3046475177455866</v>
+        <v>-0.1181004962359042</v>
       </c>
       <c r="C71" t="n">
-        <v>0.04642574483472917</v>
+        <v>-0.2823241496423203</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3510732625803157</v>
+        <v>0.164223653406416</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GLSS-SM-R108</t>
+          <t>GLSS-SM-R107</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.2423945307941151</v>
+        <v>0.04642574483472917</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3512117291129341</v>
+        <v>-0.3046475177455866</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.108817198318819</v>
+        <v>0.3510732625803157</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GLSS-SM-R109</t>
+          <t>GLSS-SM-R108</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.2378240899920144</v>
+        <v>-0.3512117291129341</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.01082190118592197</v>
+        <v>-0.2423945307941151</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2270021888060924</v>
+        <v>-0.108817198318819</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GLSS-SN-0001</t>
+          <t>GLSS-SM-R109</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.2575969176728913</v>
+        <v>-0.01082190118592197</v>
       </c>
       <c r="C74" t="n">
-        <v>0.448837223325309</v>
+        <v>-0.2378240899920144</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7064341409982003</v>
+        <v>0.2270021888060924</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GLSS-SN-0003</t>
+          <t>GLSS-SM-R110</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.2485243155234326</v>
+        <v>-0.3074856901358263</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3708897517186753</v>
+        <v>-0.2882916622201454</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6194140672421079</v>
+        <v>-0.01919402791568087</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GLSS-SN-0004</t>
+          <t>GLSS-SM-R111</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.07445856343131857</v>
+        <v>0.3262328668190944</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.02238924491874744</v>
+        <v>-0.3467720588087164</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.09684780835006601</v>
+        <v>0.6730049256278108</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GLSS-SN-0006</t>
+          <t>GLSS-SN-0001</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.2898251480225862</v>
+        <v>0.448837223325309</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3680618401331509</v>
+        <v>-0.2575969176728913</v>
       </c>
       <c r="D77" t="n">
-        <v>0.07823669211056472</v>
+        <v>0.7064341409982003</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GLSS-SN-0009</t>
+          <t>GLSS-SN-0003</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.1761033402432755</v>
+        <v>0.3708897517186753</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2012011685388693</v>
+        <v>-0.2485243155234326</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3773045087821448</v>
+        <v>0.6194140672421079</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GLSS-SN-0010</t>
+          <t>GLSS-SN-0004</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.02865707705552845</v>
+        <v>-0.02238924491874744</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.2781761542251417</v>
+        <v>0.07445856343131857</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.3068332312806701</v>
+        <v>-0.09684780835006601</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GLSS-SN-0016</t>
+          <t>GLSS-SN-0006</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.2147694468069534</v>
+        <v>0.3680618401331509</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2309263938129483</v>
+        <v>0.2898251480225862</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4456958406199017</v>
+        <v>0.07823669211056472</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TCGA-06-0125</t>
+          <t>GLSS-SN-0009</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.3996994317256232</v>
+        <v>0.2012011685388693</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.09137716260645812</v>
+        <v>-0.1761033402432755</v>
       </c>
       <c r="D81" t="n">
-        <v>0.308322269119165</v>
+        <v>0.3773045087821448</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TCGA-06-0190</t>
+          <t>GLSS-SN-0010</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.2396409509685524</v>
+        <v>-0.2781761542251417</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.2220791050676875</v>
+        <v>0.02865707705552845</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0175618459008649</v>
+        <v>-0.3068332312806701</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TCGA-19-0957</t>
+          <t>GLSS-SN-0016</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.1794940351487807</v>
+        <v>0.2309263938129483</v>
       </c>
       <c r="C83" t="n">
-        <v>0.09365839355696115</v>
+        <v>-0.2147694468069534</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2731524287057418</v>
+        <v>0.4456958406199017</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>TCGA-06-0125</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>-0.09137716260645812</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.3996994317256232</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.308322269119165</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TCGA-06-0190</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>-0.2220791050676875</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.2396409509685524</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.0175618459008649</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TCGA-19-0957</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.09365839355696115</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.1794940351487807</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.2731524287057418</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>TCGA-19-4065</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B87" t="n">
+        <v>0.03253733428895245</v>
+      </c>
+      <c r="C87" t="n">
         <v>-0.2652092860582789</v>
       </c>
-      <c r="C84" t="n">
-        <v>0.03253733428895245</v>
-      </c>
-      <c r="D84" t="n">
+      <c r="D87" t="n">
         <v>0.2977466203472314</v>
       </c>
     </row>
@@ -1790,26 +1826,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>PATIENT_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>First Recurrence</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tumor Primary</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>DELTA_RECURRENCE_SCORE</t>
         </is>
@@ -1822,10 +1858,10 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.240397942741943</v>
+      </c>
+      <c r="C2" t="n">
         <v>-0.1500761234768785</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.240397942741943</v>
       </c>
       <c r="D2" t="n">
         <v>0.3904740662188216</v>
@@ -1838,10 +1874,10 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.4213211981181357</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0.2764734625958086</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.4213211981181357</v>
       </c>
       <c r="D3" t="n">
         <v>0.6977946607139442</v>
@@ -1854,10 +1890,10 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.1041018816463418</v>
+      </c>
+      <c r="C4" t="n">
         <v>-0.2389124700544564</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1041018816463418</v>
       </c>
       <c r="D4" t="n">
         <v>0.3430143517007982</v>
@@ -1870,10 +1906,10 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.1745181502648471</v>
+      </c>
+      <c r="C5" t="n">
         <v>-0.313748353062365</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1745181502648471</v>
       </c>
       <c r="D5" t="n">
         <v>0.4882665033272121</v>
@@ -1886,10 +1922,10 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.4431521062380919</v>
+      </c>
+      <c r="C6" t="n">
         <v>-0.2535692991396751</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.4431521062380919</v>
       </c>
       <c r="D6" t="n">
         <v>0.6967214053777669</v>
@@ -1902,10 +1938,10 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>-0.1199295756593415</v>
+      </c>
+      <c r="C7" t="n">
         <v>-0.1459773140351692</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.1199295756593415</v>
       </c>
       <c r="D7" t="n">
         <v>0.02604773837582769</v>
@@ -1918,10 +1954,10 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-0.06818193829026142</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.338679588595303</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.06818193829026142</v>
       </c>
       <c r="D8" t="n">
         <v>-0.4068615268855644</v>
@@ -1934,10 +1970,10 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-0.2155618399951673</v>
+      </c>
+      <c r="C9" t="n">
         <v>-0.08361289843555031</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.2155618399951673</v>
       </c>
       <c r="D9" t="n">
         <v>-0.131948941559617</v>
@@ -1950,10 +1986,10 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-0.2254429466417733</v>
+      </c>
+      <c r="C10" t="n">
         <v>-0.2735750275974079</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.2254429466417733</v>
       </c>
       <c r="D10" t="n">
         <v>0.04813208095563454</v>
@@ -1966,10 +2002,10 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-0.1858585144416247</v>
+      </c>
+      <c r="C11" t="n">
         <v>-0.3121996700922749</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.1858585144416247</v>
       </c>
       <c r="D11" t="n">
         <v>0.1263411556506502</v>
@@ -1982,10 +2018,10 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>0.2822901815320389</v>
+      </c>
+      <c r="C12" t="n">
         <v>-0.2575719702398097</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.2822901815320389</v>
       </c>
       <c r="D12" t="n">
         <v>0.5398621517718485</v>
@@ -1998,10 +2034,10 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-0.1916952565215667</v>
+      </c>
+      <c r="C13" t="n">
         <v>-0.3792681687753456</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.1916952565215667</v>
       </c>
       <c r="D13" t="n">
         <v>0.1875729122537789</v>
@@ -2014,10 +2050,10 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>0.1854433873613601</v>
+      </c>
+      <c r="C14" t="n">
         <v>0.190599868617545</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.1854433873613601</v>
       </c>
       <c r="D14" t="n">
         <v>-0.005156481256184897</v>
@@ -2030,10 +2066,10 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0.2120321680177605</v>
+      </c>
+      <c r="C15" t="n">
         <v>-0.263503400108836</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.2120321680177605</v>
       </c>
       <c r="D15" t="n">
         <v>0.4755355681265965</v>
@@ -2046,10 +2082,10 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>-0.04550521491040738</v>
+      </c>
+      <c r="C16" t="n">
         <v>-0.01180110863191397</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.04550521491040738</v>
       </c>
       <c r="D16" t="n">
         <v>-0.03370410627849341</v>
@@ -2062,10 +2098,10 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0.09548493753193116</v>
+      </c>
+      <c r="C17" t="n">
         <v>-0.2842593539696623</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.09548493753193116</v>
       </c>
       <c r="D17" t="n">
         <v>0.3797442915015935</v>
@@ -2078,10 +2114,10 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-0.01522654780539456</v>
+      </c>
+      <c r="C18" t="n">
         <v>-0.3451595291067139</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.01522654780539456</v>
       </c>
       <c r="D18" t="n">
         <v>0.3299329813013194</v>
@@ -2094,10 +2130,10 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>0.2027758303693769</v>
+      </c>
+      <c r="C19" t="n">
         <v>-0.2064253790402321</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.2027758303693769</v>
       </c>
       <c r="D19" t="n">
         <v>0.409201209409609</v>
@@ -2110,10 +2146,10 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0.294537277274133</v>
+      </c>
+      <c r="C20" t="n">
         <v>-0.1787230932344356</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.294537277274133</v>
       </c>
       <c r="D20" t="n">
         <v>0.4732603705085686</v>
@@ -2126,10 +2162,10 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0.1904859131449045</v>
+      </c>
+      <c r="C21" t="n">
         <v>-0.1166735285906</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.1904859131449045</v>
       </c>
       <c r="D21" t="n">
         <v>0.3071594417355045</v>
@@ -2142,10 +2178,10 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>0.009123982064009883</v>
+      </c>
+      <c r="C22" t="n">
         <v>0.237884575098714</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.009123982064009883</v>
       </c>
       <c r="D22" t="n">
         <v>-0.2287605930347041</v>
@@ -2158,10 +2194,10 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-0.001284185675907046</v>
+      </c>
+      <c r="C23" t="n">
         <v>-0.23761454121298</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.001284185675907046</v>
       </c>
       <c r="D23" t="n">
         <v>0.2363303555370729</v>
@@ -2174,10 +2210,10 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>0.02517382103302068</v>
+      </c>
+      <c r="C24" t="n">
         <v>-0.1707181460121928</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.02517382103302068</v>
       </c>
       <c r="D24" t="n">
         <v>0.1958919670452135</v>
@@ -2190,10 +2226,10 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-0.06561323405303643</v>
+      </c>
+      <c r="C25" t="n">
         <v>-0.1498781359978958</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.06561323405303643</v>
       </c>
       <c r="D25" t="n">
         <v>0.08426490194485942</v>
@@ -2206,10 +2242,10 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-0.01643027180035167</v>
+      </c>
+      <c r="C26" t="n">
         <v>-0.169674736526544</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.01643027180035167</v>
       </c>
       <c r="D26" t="n">
         <v>0.1532444647261924</v>
@@ -2222,10 +2258,10 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>-0.1676058002285175</v>
+      </c>
+      <c r="C27" t="n">
         <v>-0.2448343928541279</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.1676058002285175</v>
       </c>
       <c r="D27" t="n">
         <v>0.07722859262561046</v>
@@ -2238,10 +2274,10 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0.2181889285389335</v>
+      </c>
+      <c r="C28" t="n">
         <v>-0.3547268645191287</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.2181889285389335</v>
       </c>
       <c r="D28" t="n">
         <v>0.5729157930580622</v>
@@ -2254,10 +2290,10 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0.2600100505867158</v>
+      </c>
+      <c r="C29" t="n">
         <v>-0.09443705220358006</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.2600100505867158</v>
       </c>
       <c r="D29" t="n">
         <v>0.3544471027902958</v>
@@ -2270,10 +2306,10 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>0.03390607113445931</v>
+      </c>
+      <c r="C30" t="n">
         <v>-0.2002254589768854</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.03390607113445931</v>
       </c>
       <c r="D30" t="n">
         <v>0.2341315301113447</v>
@@ -2286,10 +2322,10 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>0.0746377178750538</v>
+      </c>
+      <c r="C31" t="n">
         <v>-0.3059115785148844</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.0746377178750538</v>
       </c>
       <c r="D31" t="n">
         <v>0.3805492963899382</v>
@@ -2302,10 +2338,10 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>0.2940113528206453</v>
+      </c>
+      <c r="C32" t="n">
         <v>-0.170178435273264</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.2940113528206453</v>
       </c>
       <c r="D32" t="n">
         <v>0.4641897880939093</v>
@@ -2318,10 +2354,10 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>-0.2328361142960023</v>
+      </c>
+      <c r="C33" t="n">
         <v>-0.2222798729160098</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.2328361142960023</v>
       </c>
       <c r="D33" t="n">
         <v>-0.01055624137999256</v>
@@ -2334,10 +2370,10 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>-0.2299466189094423</v>
+      </c>
+      <c r="C34" t="n">
         <v>-0.3925134343582948</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.2299466189094423</v>
       </c>
       <c r="D34" t="n">
         <v>0.1625668154488525</v>
@@ -2350,10 +2386,10 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>-0.171768430530216</v>
+      </c>
+      <c r="C35" t="n">
         <v>0.0535955550021493</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.171768430530216</v>
       </c>
       <c r="D35" t="n">
         <v>-0.2253639855323653</v>
@@ -2366,10 +2402,10 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>0.403528959292164</v>
+      </c>
+      <c r="C36" t="n">
         <v>-0.138173420977198</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.403528959292164</v>
       </c>
       <c r="D36" t="n">
         <v>0.5417023802693621</v>
@@ -2382,10 +2418,10 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>-0.1189164035526579</v>
+      </c>
+      <c r="C37" t="n">
         <v>-0.1167391742835678</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.1189164035526579</v>
       </c>
       <c r="D37" t="n">
         <v>-0.002177229269090031</v>
@@ -2398,10 +2434,10 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>0.3217665587828171</v>
+      </c>
+      <c r="C38" t="n">
         <v>-0.2362411491461037</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.3217665587828171</v>
       </c>
       <c r="D38" t="n">
         <v>0.5580077079289207</v>
@@ -2414,10 +2450,10 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>-0.1593925529787303</v>
+      </c>
+      <c r="C39" t="n">
         <v>-0.1311696188669709</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.1593925529787303</v>
       </c>
       <c r="D39" t="n">
         <v>-0.02822293411175941</v>
@@ -2430,10 +2466,10 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>0.02421054206770556</v>
+      </c>
+      <c r="C40" t="n">
         <v>-0.3119282977657173</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.02421054206770556</v>
       </c>
       <c r="D40" t="n">
         <v>0.3361388398334229</v>
@@ -2446,10 +2482,10 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>-0.3683494893489501</v>
+      </c>
+      <c r="C41" t="n">
         <v>-0.3318708521615391</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.3683494893489501</v>
       </c>
       <c r="D41" t="n">
         <v>-0.03647863718741096</v>
@@ -2462,10 +2498,10 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>0.07740936665173415</v>
+      </c>
+      <c r="C42" t="n">
         <v>-0.0366035140612041</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.07740936665173415</v>
       </c>
       <c r="D42" t="n">
         <v>0.1140128807129382</v>
@@ -2478,10 +2514,10 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>0.04409624032524612</v>
+      </c>
+      <c r="C43" t="n">
         <v>-0.2348577567185383</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.04409624032524612</v>
       </c>
       <c r="D43" t="n">
         <v>0.2789539970437844</v>
@@ -2494,10 +2530,10 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>-0.1693948040430185</v>
+      </c>
+      <c r="C44" t="n">
         <v>-0.2262223090047014</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.1693948040430185</v>
       </c>
       <c r="D44" t="n">
         <v>0.05682750496168287</v>
@@ -2510,10 +2546,10 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>-0.3584373639913</v>
+      </c>
+      <c r="C45" t="n">
         <v>-0.09053534887067188</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.3584373639913</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2679020151206281</v>
@@ -2526,10 +2562,10 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>-0.1597541493252341</v>
+      </c>
+      <c r="C46" t="n">
         <v>-0.203923831416286</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.1597541493252341</v>
       </c>
       <c r="D46" t="n">
         <v>0.04416968209105182</v>
@@ -2542,10 +2578,10 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>0.06591725674659032</v>
+      </c>
+      <c r="C47" t="n">
         <v>-0.1671454317786639</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.06591725674659032</v>
       </c>
       <c r="D47" t="n">
         <v>0.2330626885252542</v>
@@ -2558,10 +2594,10 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>0.2925491890111084</v>
+      </c>
+      <c r="C48" t="n">
         <v>-0.3291747442260283</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.2925491890111084</v>
       </c>
       <c r="D48" t="n">
         <v>0.6217239332371367</v>
@@ -2574,10 +2610,10 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>0.1863883679778391</v>
+      </c>
+      <c r="C49" t="n">
         <v>-0.2353337552595551</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.1863883679778391</v>
       </c>
       <c r="D49" t="n">
         <v>0.4217221232373942</v>
@@ -2586,272 +2622,304 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GLSS-SM-R099</t>
+          <t>GLSS-SM-R095</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1421079540557695</v>
+        <v>0.3354024800563348</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2032358262635371</v>
+        <v>-0.2674284726875144</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3453437803193067</v>
+        <v>0.6028309527438491</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GLSS-SM-R100</t>
+          <t>GLSS-SM-R099</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1917551586475986</v>
+        <v>0.2032358262635371</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.03854988988495561</v>
+        <v>-0.1421079540557695</v>
       </c>
       <c r="D51" t="n">
-        <v>0.153205268762643</v>
+        <v>0.3453437803193067</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GLSS-SM-R103</t>
+          <t>GLSS-SM-R100</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2750077146625198</v>
+        <v>-0.03854988988495561</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2540674285237414</v>
+        <v>-0.1917551586475986</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5290751431862613</v>
+        <v>0.153205268762643</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GLSS-SM-R106</t>
+          <t>GLSS-SM-R103</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2823241496423203</v>
+        <v>0.2540674285237414</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1181004962359042</v>
+        <v>-0.2750077146625198</v>
       </c>
       <c r="D53" t="n">
-        <v>0.164223653406416</v>
+        <v>0.5290751431862613</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GLSS-SM-R107</t>
+          <t>GLSS-SM-R106</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3046475177455866</v>
+        <v>-0.1181004962359042</v>
       </c>
       <c r="C54" t="n">
-        <v>0.04642574483472917</v>
+        <v>-0.2823241496423203</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3510732625803157</v>
+        <v>0.164223653406416</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GLSS-SM-R108</t>
+          <t>GLSS-SM-R107</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2423945307941151</v>
+        <v>0.04642574483472917</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.3512117291129341</v>
+        <v>-0.3046475177455866</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.108817198318819</v>
+        <v>0.3510732625803157</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GLSS-SM-R109</t>
+          <t>GLSS-SM-R108</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2378240899920144</v>
+        <v>-0.3512117291129341</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.01082190118592197</v>
+        <v>-0.2423945307941151</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2270021888060924</v>
+        <v>-0.108817198318819</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GLSS-SN-0001</t>
+          <t>GLSS-SM-R109</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2575969176728913</v>
+        <v>-0.01082190118592197</v>
       </c>
       <c r="C57" t="n">
-        <v>0.448837223325309</v>
+        <v>-0.2378240899920144</v>
       </c>
       <c r="D57" t="n">
-        <v>0.7064341409982003</v>
+        <v>0.2270021888060924</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GLSS-SN-0003</t>
+          <t>GLSS-SM-R110</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2485243155234326</v>
+        <v>-0.3074856901358263</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3708897517186753</v>
+        <v>-0.2882916622201454</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6194140672421079</v>
+        <v>-0.01919402791568087</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GLSS-SN-0004</t>
+          <t>GLSS-SN-0001</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.07445856343131857</v>
+        <v>0.448837223325309</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.02238924491874744</v>
+        <v>-0.2575969176728913</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.09684780835006601</v>
+        <v>0.7064341409982003</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GLSS-SN-0006</t>
+          <t>GLSS-SN-0003</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2898251480225862</v>
+        <v>0.3708897517186753</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3680618401331509</v>
+        <v>-0.2485243155234326</v>
       </c>
       <c r="D60" t="n">
-        <v>0.07823669211056472</v>
+        <v>0.6194140672421079</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GLSS-SN-0009</t>
+          <t>GLSS-SN-0004</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1761033402432755</v>
+        <v>-0.02238924491874744</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2012011685388693</v>
+        <v>0.07445856343131857</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3773045087821448</v>
+        <v>-0.09684780835006601</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GLSS-SN-0010</t>
+          <t>GLSS-SN-0006</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.02865707705552845</v>
+        <v>0.3680618401331509</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2781761542251417</v>
+        <v>0.2898251480225862</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.3068332312806701</v>
+        <v>0.07823669211056472</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GLSS-SN-0016</t>
+          <t>GLSS-SN-0009</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2147694468069534</v>
+        <v>0.2012011685388693</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2309263938129483</v>
+        <v>-0.1761033402432755</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4456958406199017</v>
+        <v>0.3773045087821448</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TCGA-06-0190</t>
+          <t>GLSS-SN-0010</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2396409509685524</v>
+        <v>-0.2781761542251417</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2220791050676875</v>
+        <v>0.02865707705552845</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0175618459008649</v>
+        <v>-0.3068332312806701</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TCGA-19-0957</t>
+          <t>GLSS-SN-0016</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.1794940351487807</v>
+        <v>0.2309263938129483</v>
       </c>
       <c r="C65" t="n">
-        <v>0.09365839355696115</v>
+        <v>-0.2147694468069534</v>
       </c>
       <c r="D65" t="n">
-        <v>0.2731524287057418</v>
+        <v>0.4456958406199017</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>TCGA-06-0190</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.2220791050676875</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.2396409509685524</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0175618459008649</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TCGA-19-0957</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.09365839355696115</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.1794940351487807</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.2731524287057418</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>TCGA-19-4065</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B68" t="n">
+        <v>0.03253733428895245</v>
+      </c>
+      <c r="C68" t="n">
         <v>-0.2652092860582789</v>
       </c>
-      <c r="C66" t="n">
-        <v>0.03253733428895245</v>
-      </c>
-      <c r="D66" t="n">
+      <c r="D68" t="n">
         <v>0.2977466203472314</v>
       </c>
     </row>

--- a/results/recurrence/glass_recurrence_score_standard_treatment.xlsx
+++ b/results/recurrence/glass_recurrence_score_standard_treatment.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,22 +430,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PATIENT_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>First Recurrence</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tumor Primary</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>DELTA_RECURRENCE_SCORE</t>
         </is>
@@ -1830,22 +1842,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PATIENT_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>First Recurrence</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tumor Primary</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>DELTA_RECURRENCE_SCORE</t>
         </is>
